--- a/template_mrf.xlsx
+++ b/template_mrf.xlsx
@@ -5,16 +5,19 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nokia-my.sharepoint.com/personal/edgar_peralta_ext_nokia_com/Documents/New folder/SPBD RESI/MRF/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\N-20W1PF3VP3VC-Data\rabanes\Documents\mrf automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7310B61C-C040-4F44-945F-15FD27989B03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3616E37-4C87-43E8-9977-48B80443EEAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D0198B82-F0F5-48E3-BCED-1601A3552D56}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE (MF-2)" sheetId="35" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'SAMPLE (MF-2)'!$A$1:$G$56</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="94">
   <si>
     <t>Material Request Form</t>
   </si>
@@ -204,12 +207,6 @@
     <t>Signature:</t>
   </si>
   <si>
-    <t>Signature :</t>
-  </si>
-  <si>
-    <t>Date :</t>
-  </si>
-  <si>
     <t xml:space="preserve">Date: </t>
   </si>
   <si>
@@ -282,9 +279,6 @@
     <t>32 for 2 LT Cards</t>
   </si>
   <si>
-    <t>PLAID  - SITE NAME</t>
-  </si>
-  <si>
     <t>3FE77035BA</t>
   </si>
   <si>
@@ -303,13 +297,28 @@
     <t>LOCAL MATERIALS/ ACCESSORIES</t>
   </si>
   <si>
-    <t>Received by: ENOVELL Team</t>
-  </si>
-  <si>
     <t>Request by: Kevin Colmo/ John Carlo Rabanes</t>
   </si>
   <si>
     <t>NOKIA-FN_06232026-001_PLAID-SITE NAME_MF2_SUBCON</t>
+  </si>
+  <si>
+    <t>[PLAID  - SITE NAME]</t>
+  </si>
+  <si>
+    <t>[CITY]</t>
+  </si>
+  <si>
+    <t>[SITE_ADD]</t>
+  </si>
+  <si>
+    <t>Received by: [RECEIVED BY]</t>
+  </si>
+  <si>
+    <t>Signature : [ESIG]</t>
+  </si>
+  <si>
+    <t>Date : [DATE_GENERATED]</t>
   </si>
 </sst>
 </file>
@@ -755,7 +764,7 @@
       <alignment vertical="top"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyProtection="1">
       <protection locked="0"/>
@@ -950,6 +959,81 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
@@ -958,38 +1042,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -998,59 +1050,17 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1557,29 +1567,30 @@
   <dimension ref="A1:L54"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.54296875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="58" style="1" customWidth="1"/>
+    <col min="1" max="1" width="21" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.54296875" style="1" customWidth="1"/>
     <col min="3" max="3" width="17.453125" style="1" customWidth="1"/>
     <col min="4" max="4" width="18.7265625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.54296875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="27.453125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.1796875" style="1"/>
+    <col min="8" max="8" width="17.6328125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="E1" s="16"/>
     </row>
     <row r="2" spans="1:12" ht="25" x14ac:dyDescent="0.5">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
     </row>
     <row r="3" spans="1:12" ht="25" x14ac:dyDescent="0.5">
       <c r="C3" s="36"/>
@@ -1609,12 +1620,12 @@
       <c r="D6" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="74">
+      <c r="E6" s="87">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
-      </c>
-      <c r="F6" s="74"/>
-      <c r="G6" s="74"/>
+        <v>46197</v>
+      </c>
+      <c r="F6" s="87"/>
+      <c r="G6" s="87"/>
     </row>
     <row r="7" spans="1:12" ht="15" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
@@ -1634,9 +1645,11 @@
       <c r="D8" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="83"/>
-      <c r="F8" s="83"/>
-      <c r="G8" s="83"/>
+      <c r="E8" s="70" t="s">
+        <v>89</v>
+      </c>
+      <c r="F8" s="70"/>
+      <c r="G8" s="70"/>
     </row>
     <row r="9" spans="1:12" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>
@@ -1656,11 +1669,11 @@
       <c r="D10" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="83" t="s">
-        <v>82</v>
-      </c>
-      <c r="F10" s="83"/>
-      <c r="G10" s="83"/>
+      <c r="E10" s="70" t="s">
+        <v>88</v>
+      </c>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
       <c r="H10" s="19"/>
       <c r="I10" s="19"/>
       <c r="J10" s="19"/>
@@ -1672,9 +1685,11 @@
       <c r="B11" s="16"/>
       <c r="C11" s="17"/>
       <c r="D11" s="10"/>
-      <c r="E11" s="75"/>
-      <c r="F11" s="75"/>
-      <c r="G11" s="75"/>
+      <c r="E11" s="90" t="s">
+        <v>90</v>
+      </c>
+      <c r="F11" s="90"/>
+      <c r="G11" s="90"/>
       <c r="H11" s="19"/>
       <c r="I11" s="19"/>
       <c r="J11" s="19"/>
@@ -1690,9 +1705,9 @@
       <c r="D12" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="76"/>
-      <c r="F12" s="76"/>
-      <c r="G12" s="76"/>
+      <c r="E12" s="91"/>
+      <c r="F12" s="91"/>
+      <c r="G12" s="91"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
@@ -1714,23 +1729,23 @@
       <c r="L13" s="19"/>
     </row>
     <row r="14" spans="1:12" s="24" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="77" t="s">
+      <c r="A14" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="78" t="s">
+      <c r="B14" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="78" t="s">
+      <c r="C14" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="78" t="s">
+      <c r="D14" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="79"/>
-      <c r="F14" s="78" t="s">
+      <c r="E14" s="72"/>
+      <c r="F14" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="G14" s="78"/>
+      <c r="G14" s="71"/>
       <c r="H14" s="23"/>
       <c r="I14" s="23"/>
       <c r="J14" s="23"/>
@@ -1738,13 +1753,13 @@
       <c r="L14" s="23"/>
     </row>
     <row r="15" spans="1:12" s="24" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="77"/>
-      <c r="B15" s="78"/>
-      <c r="C15" s="79"/>
-      <c r="D15" s="79"/>
-      <c r="E15" s="79"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="78"/>
+      <c r="A15" s="88"/>
+      <c r="B15" s="71"/>
+      <c r="C15" s="72"/>
+      <c r="D15" s="72"/>
+      <c r="E15" s="72"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
       <c r="H15" s="23"/>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
@@ -1752,17 +1767,17 @@
       <c r="L15" s="23"/>
     </row>
     <row r="16" spans="1:12" s="24" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="77"/>
-      <c r="B16" s="78"/>
-      <c r="C16" s="79"/>
-      <c r="D16" s="78" t="s">
+      <c r="A16" s="88"/>
+      <c r="B16" s="71"/>
+      <c r="C16" s="72"/>
+      <c r="D16" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="78"/>
-      <c r="F16" s="78" t="s">
+      <c r="E16" s="71"/>
+      <c r="F16" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="G16" s="79"/>
+      <c r="G16" s="72"/>
       <c r="H16" s="23"/>
       <c r="I16" s="23"/>
       <c r="J16" s="23"/>
@@ -1770,9 +1785,9 @@
       <c r="L16" s="23"/>
     </row>
     <row r="17" spans="1:12" s="24" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="77"/>
-      <c r="B17" s="78"/>
-      <c r="C17" s="79"/>
+      <c r="A17" s="88"/>
+      <c r="B17" s="71"/>
+      <c r="C17" s="72"/>
       <c r="D17" s="35" t="s">
         <v>15</v>
       </c>
@@ -1796,7 +1811,7 @@
         <v>27</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C18" s="40"/>
       <c r="D18" s="41">
@@ -1813,10 +1828,10 @@
     </row>
     <row r="19" spans="1:12" s="24" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="56" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C19" s="40"/>
       <c r="D19" s="41">
@@ -1833,10 +1848,10 @@
     </row>
     <row r="20" spans="1:12" s="24" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="56" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C20" s="40"/>
       <c r="D20" s="41">
@@ -1856,7 +1871,7 @@
         <v>28</v>
       </c>
       <c r="B21" s="37" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C21" s="40"/>
       <c r="D21" s="41">
@@ -1876,18 +1891,18 @@
         <v>29</v>
       </c>
       <c r="B22" s="56" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C22" s="40"/>
       <c r="D22" s="41">
         <v>8</v>
       </c>
       <c r="E22" s="42"/>
-      <c r="F22" s="85" t="s">
-        <v>78</v>
-      </c>
+      <c r="F22" s="89"/>
       <c r="G22" s="42"/>
-      <c r="H22" s="23"/>
+      <c r="H22" s="64" t="s">
+        <v>76</v>
+      </c>
       <c r="I22" s="23"/>
       <c r="J22" s="23"/>
       <c r="K22" s="23"/>
@@ -1895,21 +1910,21 @@
     </row>
     <row r="23" spans="1:12" s="24" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="56" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B23" s="56" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C23" s="40"/>
       <c r="D23" s="41">
         <v>8</v>
       </c>
       <c r="E23" s="42"/>
-      <c r="F23" s="85" t="s">
-        <v>78</v>
-      </c>
+      <c r="F23" s="89"/>
       <c r="G23" s="42"/>
-      <c r="H23" s="23"/>
+      <c r="H23" s="64" t="s">
+        <v>76</v>
+      </c>
       <c r="I23" s="23"/>
       <c r="J23" s="23"/>
       <c r="K23" s="23"/>
@@ -1920,16 +1935,16 @@
         <v>30</v>
       </c>
       <c r="B24" s="37" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C24" s="40"/>
       <c r="D24" s="41">
         <v>2</v>
       </c>
       <c r="E24" s="60"/>
-      <c r="F24" s="84"/>
-      <c r="G24" s="84"/>
-      <c r="H24" s="23"/>
+      <c r="F24" s="89"/>
+      <c r="G24" s="63"/>
+      <c r="H24" s="63"/>
       <c r="I24" s="23"/>
       <c r="J24" s="23"/>
       <c r="K24" s="23"/>
@@ -1940,33 +1955,33 @@
         <v>31</v>
       </c>
       <c r="B25" s="37" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C25" s="40"/>
       <c r="D25" s="41">
         <v>1</v>
       </c>
       <c r="E25" s="60"/>
-      <c r="F25" s="61" t="s">
-        <v>79</v>
-      </c>
-      <c r="G25" s="84"/>
-      <c r="H25" s="23"/>
+      <c r="F25" s="89"/>
+      <c r="G25" s="63"/>
+      <c r="H25" s="61" t="s">
+        <v>77</v>
+      </c>
       <c r="I25" s="23"/>
       <c r="J25" s="23"/>
       <c r="K25" s="23"/>
       <c r="L25" s="23"/>
     </row>
     <row r="26" spans="1:12" s="24" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="88" t="s">
-        <v>88</v>
-      </c>
-      <c r="B26" s="89"/>
-      <c r="C26" s="89"/>
-      <c r="D26" s="89"/>
-      <c r="E26" s="89"/>
-      <c r="F26" s="89"/>
-      <c r="G26" s="90"/>
+      <c r="A26" s="81" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" s="82"/>
+      <c r="C26" s="82"/>
+      <c r="D26" s="82"/>
+      <c r="E26" s="82"/>
+      <c r="F26" s="82"/>
+      <c r="G26" s="83"/>
       <c r="H26" s="23"/>
       <c r="I26" s="23"/>
       <c r="J26" s="23"/>
@@ -1975,10 +1990,10 @@
     </row>
     <row r="27" spans="1:12" s="24" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="37" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B27" s="37" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C27" s="44"/>
       <c r="D27" s="48">
@@ -2011,10 +2026,10 @@
     </row>
     <row r="29" spans="1:12" s="24" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="62" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C29" s="47"/>
       <c r="D29" s="48">
@@ -2181,17 +2196,17 @@
       <c r="E38" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="F38" s="86" t="s">
-        <v>80</v>
+      <c r="F38" s="65" t="s">
+        <v>78</v>
       </c>
       <c r="G38" s="25"/>
     </row>
     <row r="39" spans="1:8" s="24" customFormat="1" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="37" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B39" s="37" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C39" s="47"/>
       <c r="D39" s="54">
@@ -2200,17 +2215,17 @@
       <c r="E39" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="F39" s="86" t="s">
-        <v>81</v>
+      <c r="F39" s="65" t="s">
+        <v>79</v>
       </c>
       <c r="G39" s="25"/>
     </row>
     <row r="40" spans="1:8" ht="26.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="37" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B40" s="37" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C40" s="29"/>
       <c r="D40" s="51">
@@ -2224,27 +2239,27 @@
     </row>
     <row r="41" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="37" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B41" s="37" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C41" s="29"/>
       <c r="D41" s="51">
         <v>1</v>
       </c>
       <c r="E41" s="45"/>
-      <c r="F41" s="87" t="s">
-        <v>85</v>
+      <c r="F41" s="66" t="s">
+        <v>82</v>
       </c>
       <c r="G41" s="32"/>
     </row>
     <row r="42" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="37" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B42" s="37" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C42" s="55"/>
       <c r="D42" s="51">
@@ -2276,63 +2291,63 @@
       <c r="A45" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="B45" s="65" t="s">
+      <c r="B45" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="C45" s="67" t="s">
-        <v>89</v>
-      </c>
-      <c r="D45" s="68"/>
-      <c r="E45" s="68"/>
-      <c r="F45" s="68"/>
-      <c r="G45" s="69"/>
+      <c r="C45" s="75" t="s">
+        <v>91</v>
+      </c>
+      <c r="D45" s="76"/>
+      <c r="E45" s="76"/>
+      <c r="F45" s="76"/>
+      <c r="G45" s="77"/>
     </row>
     <row r="46" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="63" t="s">
-        <v>90</v>
-      </c>
-      <c r="B46" s="66"/>
-      <c r="C46" s="70"/>
-      <c r="D46" s="71"/>
-      <c r="E46" s="71"/>
-      <c r="F46" s="71"/>
-      <c r="G46" s="72"/>
+      <c r="A46" s="84" t="s">
+        <v>86</v>
+      </c>
+      <c r="B46" s="74"/>
+      <c r="C46" s="78"/>
+      <c r="D46" s="79"/>
+      <c r="E46" s="79"/>
+      <c r="F46" s="79"/>
+      <c r="G46" s="80"/>
     </row>
     <row r="47" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="64"/>
-      <c r="B47" s="65" t="s">
+      <c r="A47" s="85"/>
+      <c r="B47" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="C47" s="67" t="s">
-        <v>56</v>
-      </c>
-      <c r="D47" s="68"/>
-      <c r="E47" s="68"/>
-      <c r="F47" s="68"/>
-      <c r="G47" s="69"/>
+      <c r="C47" s="75" t="s">
+        <v>92</v>
+      </c>
+      <c r="D47" s="76"/>
+      <c r="E47" s="76"/>
+      <c r="F47" s="76"/>
+      <c r="G47" s="77"/>
     </row>
     <row r="48" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="B48" s="66"/>
-      <c r="C48" s="70"/>
-      <c r="D48" s="71"/>
-      <c r="E48" s="71"/>
-      <c r="F48" s="71"/>
-      <c r="G48" s="72"/>
+        <v>56</v>
+      </c>
+      <c r="B48" s="74"/>
+      <c r="C48" s="78"/>
+      <c r="D48" s="79"/>
+      <c r="E48" s="79"/>
+      <c r="F48" s="79"/>
+      <c r="G48" s="80"/>
     </row>
     <row r="49" spans="2:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="C49" s="80" t="s">
-        <v>57</v>
-      </c>
-      <c r="D49" s="81"/>
-      <c r="E49" s="81"/>
-      <c r="F49" s="81"/>
-      <c r="G49" s="82"/>
+      <c r="C49" s="67" t="s">
+        <v>93</v>
+      </c>
+      <c r="D49" s="68"/>
+      <c r="E49" s="68"/>
+      <c r="F49" s="68"/>
+      <c r="G49" s="69"/>
     </row>
     <row r="51" spans="2:7" ht="13" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="52" spans="2:7" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2355,12 +2370,21 @@
         <v>25</v>
       </c>
       <c r="F54" s="30" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G54" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="E11:G12"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="D14:E15"/>
+    <mergeCell ref="F14:G15"/>
+    <mergeCell ref="D16:E16"/>
     <mergeCell ref="C49:G49"/>
     <mergeCell ref="E8:G8"/>
     <mergeCell ref="E10:G10"/>
@@ -2371,15 +2395,6 @@
     <mergeCell ref="A46:A47"/>
     <mergeCell ref="B47:B48"/>
     <mergeCell ref="C47:G48"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="E11:G12"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="D14:E15"/>
-    <mergeCell ref="F14:G15"/>
-    <mergeCell ref="D16:E16"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <conditionalFormatting sqref="A18">
@@ -2415,14 +2430,14 @@
   <conditionalFormatting sqref="A39">
     <cfRule type="duplicateValues" dxfId="3" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A44">
-    <cfRule type="duplicateValues" dxfId="2" priority="14"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A41">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A42">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A44">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
   </conditionalFormatting>
   <pageMargins left="0.23599999999999999" right="0.23599999999999999" top="0.35399999999999998" bottom="0.748" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="58" orientation="portrait" r:id="rId1"/>
@@ -2431,21 +2446,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="34c87397-5fc1-491e-85e7-d6110dbe9cbd" ContentTypeId="0x010100CE50E52E7543470BBDD3827FE50C59CB" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<customXsn xmlns="http://schemas.microsoft.com/office/2006/metadata/customXsn">
-  <xsnLocation/>
-  <cached>True</cached>
-  <openByDefault>True</openByDefault>
-  <xsnScope/>
-</customXsn>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -2495,33 +2495,22 @@
 </spe:Receivers>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<customXsn xmlns="http://schemas.microsoft.com/office/2006/metadata/customXsn">
+  <xsnLocation/>
+  <cached>True</cached>
+  <openByDefault>True</openByDefault>
+  <xsnScope/>
+</customXsn>
 </file>
 
-<file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Owner xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105" xsi:nil="true"/>
-    <DocumentType xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105">Description</DocumentType>
-    <NokiaConfidentiality xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105">Nokia Internal Use</NokiaConfidentiality>
-    <HideFromDelve xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105">false</HideFromDelve>
-    <EXECUTE_x0020_Content xmlns="31aacdf4-fb95-42ec-80aa-6fc76e563ffe" xsi:nil="true"/>
-    <_dlc_DocId xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105">4NIMP5LIAM4P-487227298-104996</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105">
-      <Url>https://nokia.sharepoint.com/sites/FN_EXECUTE_Projects_01/19.PH.891566/_layouts/15/DocIdRedir.aspx?ID=4NIMP5LIAM4P-487227298-104996</Url>
-      <Description>4NIMP5LIAM4P-487227298-104996</Description>
-    </_dlc_DocIdUrl>
-  </documentManagement>
-</p:properties>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="34c87397-5fc1-491e-85e7-d6110dbe9cbd" ContentTypeId="0x010100CE50E52E7543470BBDD3827FE50C59CB" PreviousValue="false"/>
 </file>
 
-<file path=customXml/item6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Nokia Document" ma:contentTypeID="0x010100CE50E52E7543470BBDD3827FE50C59CB0070987D5F99DEA046A5556E9784C3DBB3" ma:contentTypeVersion="0" ma:contentTypeDescription="Create Nokia Word Document" ma:contentTypeScope="" ma:versionID="39bab26bba4b4695d71013085a059bf5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="71c5aaf6-e6ce-465b-b873-5148d2a4c105" xmlns:ns3="31aacdf4-fb95-42ec-80aa-6fc76e563ffe" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="987c3fb9869095ea02b628ded8d4e70e" ns2:_="" ns3:_="">
     <xsd:import namespace="71c5aaf6-e6ce-465b-b873-5148d2a4c105"/>
@@ -2737,10 +2726,36 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Owner xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105" xsi:nil="true"/>
+    <DocumentType xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105">Description</DocumentType>
+    <NokiaConfidentiality xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105">Nokia Internal Use</NokiaConfidentiality>
+    <HideFromDelve xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105">false</HideFromDelve>
+    <EXECUTE_x0020_Content xmlns="31aacdf4-fb95-42ec-80aa-6fc76e563ffe" xsi:nil="true"/>
+    <_dlc_DocId xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105">4NIMP5LIAM4P-487227298-104996</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105">
+      <Url>https://nokia.sharepoint.com/sites/FN_EXECUTE_Projects_01/19.PH.891566/_layouts/15/DocIdRedir.aspx?ID=4NIMP5LIAM4P-487227298-104996</Url>
+      <Description>4NIMP5LIAM4P-487227298-104996</Description>
+    </_dlc_DocIdUrl>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item6.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A291274A-4EA0-4E57-B629-E0B27FF3F3C9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7757C609-38DF-42A4-8039-8FE07EDFDC95}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2754,33 +2769,14 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7757C609-38DF-42A4-8039-8FE07EDFDC95}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A291274A-4EA0-4E57-B629-E0B27FF3F3C9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6B4300D-9EFA-4008-840F-6108E8E828B4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4695F569-C332-4377-B336-958B36C084BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="71c5aaf6-e6ce-465b-b873-5148d2a4c105"/>
-    <ds:schemaRef ds:uri="31aacdf4-fb95-42ec-80aa-6fc76e563ffe"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps6.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECC18FBB-FF2E-44EB-8E2A-7526D9399CAC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2799,6 +2795,25 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4695F569-C332-4377-B336-958B36C084BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="71c5aaf6-e6ce-465b-b873-5148d2a4c105"/>
+    <ds:schemaRef ds:uri="31aacdf4-fb95-42ec-80aa-6fc76e563ffe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps6.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6B4300D-9EFA-4008-840F-6108E8E828B4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{5d471751-9675-428d-917b-70f44f9630b0}" enabled="0" method="" siteId="{5d471751-9675-428d-917b-70f44f9630b0}" removed="1"/>

--- a/template_mrf.xlsx
+++ b/template_mrf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\N-20W1PF3VP3VC-Data\rabanes\Documents\mrf automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3616E37-4C87-43E8-9977-48B80443EEAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FBD3B9D-2D7B-4769-9CFF-A6848F2F5312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D0198B82-F0F5-48E3-BCED-1601A3552D56}"/>
   </bookViews>

--- a/template_mrf.xlsx
+++ b/template_mrf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\N-20W1PF3VP3VC-Data\rabanes\Documents\mrf automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FBD3B9D-2D7B-4769-9CFF-A6848F2F5312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12DBB0C4-4B19-4504-B3D9-D95D43C98AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D0198B82-F0F5-48E3-BCED-1601A3552D56}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="95">
   <si>
     <t>Material Request Form</t>
   </si>
@@ -315,10 +315,13 @@
     <t>Received by: [RECEIVED BY]</t>
   </si>
   <si>
-    <t>Signature : [ESIG]</t>
-  </si>
-  <si>
     <t>Date : [DATE_GENERATED]</t>
+  </si>
+  <si>
+    <t>Signature :</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [ESIG]</t>
   </si>
 </sst>
 </file>
@@ -973,6 +976,30 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -989,10 +1016,6 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
@@ -1040,26 +1063,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1582,15 +1585,15 @@
       <c r="E1" s="16"/>
     </row>
     <row r="2" spans="1:12" ht="25" x14ac:dyDescent="0.5">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="86"/>
-      <c r="C2" s="86"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="86"/>
-      <c r="G2" s="86"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
     </row>
     <row r="3" spans="1:12" ht="25" x14ac:dyDescent="0.5">
       <c r="C3" s="36"/>
@@ -1620,12 +1623,12 @@
       <c r="D6" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="87">
+      <c r="E6" s="69">
         <f ca="1">TODAY()</f>
         <v>46197</v>
       </c>
-      <c r="F6" s="87"/>
-      <c r="G6" s="87"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
     </row>
     <row r="7" spans="1:12" ht="15" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
@@ -1645,11 +1648,11 @@
       <c r="D8" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="70" t="s">
+      <c r="E8" s="78" t="s">
         <v>89</v>
       </c>
-      <c r="F8" s="70"/>
-      <c r="G8" s="70"/>
+      <c r="F8" s="78"/>
+      <c r="G8" s="78"/>
     </row>
     <row r="9" spans="1:12" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>
@@ -1669,11 +1672,11 @@
       <c r="D10" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="70" t="s">
+      <c r="E10" s="78" t="s">
         <v>88</v>
       </c>
-      <c r="F10" s="70"/>
-      <c r="G10" s="70"/>
+      <c r="F10" s="78"/>
+      <c r="G10" s="78"/>
       <c r="H10" s="19"/>
       <c r="I10" s="19"/>
       <c r="J10" s="19"/>
@@ -1685,11 +1688,11 @@
       <c r="B11" s="16"/>
       <c r="C11" s="17"/>
       <c r="D11" s="10"/>
-      <c r="E11" s="90" t="s">
+      <c r="E11" s="70" t="s">
         <v>90</v>
       </c>
-      <c r="F11" s="90"/>
-      <c r="G11" s="90"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
       <c r="H11" s="19"/>
       <c r="I11" s="19"/>
       <c r="J11" s="19"/>
@@ -1705,9 +1708,9 @@
       <c r="D12" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="91"/>
-      <c r="F12" s="91"/>
-      <c r="G12" s="91"/>
+      <c r="E12" s="71"/>
+      <c r="F12" s="71"/>
+      <c r="G12" s="71"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
@@ -1729,23 +1732,23 @@
       <c r="L13" s="19"/>
     </row>
     <row r="14" spans="1:12" s="24" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="88" t="s">
+      <c r="A14" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="71" t="s">
+      <c r="B14" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="71" t="s">
+      <c r="C14" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="71" t="s">
+      <c r="D14" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="72"/>
-      <c r="F14" s="71" t="s">
+      <c r="E14" s="74"/>
+      <c r="F14" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="G14" s="71"/>
+      <c r="G14" s="73"/>
       <c r="H14" s="23"/>
       <c r="I14" s="23"/>
       <c r="J14" s="23"/>
@@ -1753,13 +1756,13 @@
       <c r="L14" s="23"/>
     </row>
     <row r="15" spans="1:12" s="24" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="88"/>
-      <c r="B15" s="71"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="72"/>
-      <c r="E15" s="72"/>
-      <c r="F15" s="71"/>
-      <c r="G15" s="71"/>
+      <c r="A15" s="72"/>
+      <c r="B15" s="73"/>
+      <c r="C15" s="74"/>
+      <c r="D15" s="74"/>
+      <c r="E15" s="74"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="73"/>
       <c r="H15" s="23"/>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
@@ -1767,17 +1770,17 @@
       <c r="L15" s="23"/>
     </row>
     <row r="16" spans="1:12" s="24" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="88"/>
-      <c r="B16" s="71"/>
-      <c r="C16" s="72"/>
-      <c r="D16" s="71" t="s">
+      <c r="A16" s="72"/>
+      <c r="B16" s="73"/>
+      <c r="C16" s="74"/>
+      <c r="D16" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="71"/>
-      <c r="F16" s="71" t="s">
+      <c r="E16" s="73"/>
+      <c r="F16" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="G16" s="72"/>
+      <c r="G16" s="74"/>
       <c r="H16" s="23"/>
       <c r="I16" s="23"/>
       <c r="J16" s="23"/>
@@ -1785,9 +1788,9 @@
       <c r="L16" s="23"/>
     </row>
     <row r="17" spans="1:12" s="24" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="88"/>
-      <c r="B17" s="71"/>
-      <c r="C17" s="72"/>
+      <c r="A17" s="72"/>
+      <c r="B17" s="73"/>
+      <c r="C17" s="74"/>
       <c r="D17" s="35" t="s">
         <v>15</v>
       </c>
@@ -1898,7 +1901,7 @@
         <v>8</v>
       </c>
       <c r="E22" s="42"/>
-      <c r="F22" s="89"/>
+      <c r="F22" s="67"/>
       <c r="G22" s="42"/>
       <c r="H22" s="64" t="s">
         <v>76</v>
@@ -1920,7 +1923,7 @@
         <v>8</v>
       </c>
       <c r="E23" s="42"/>
-      <c r="F23" s="89"/>
+      <c r="F23" s="67"/>
       <c r="G23" s="42"/>
       <c r="H23" s="64" t="s">
         <v>76</v>
@@ -1942,7 +1945,7 @@
         <v>2</v>
       </c>
       <c r="E24" s="60"/>
-      <c r="F24" s="89"/>
+      <c r="F24" s="67"/>
       <c r="G24" s="63"/>
       <c r="H24" s="63"/>
       <c r="I24" s="23"/>
@@ -1962,7 +1965,7 @@
         <v>1</v>
       </c>
       <c r="E25" s="60"/>
-      <c r="F25" s="89"/>
+      <c r="F25" s="67"/>
       <c r="G25" s="63"/>
       <c r="H25" s="61" t="s">
         <v>77</v>
@@ -1973,15 +1976,15 @@
       <c r="L25" s="23"/>
     </row>
     <row r="26" spans="1:12" s="24" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="81" t="s">
+      <c r="A26" s="87" t="s">
         <v>85</v>
       </c>
-      <c r="B26" s="82"/>
-      <c r="C26" s="82"/>
-      <c r="D26" s="82"/>
-      <c r="E26" s="82"/>
-      <c r="F26" s="82"/>
-      <c r="G26" s="83"/>
+      <c r="B26" s="88"/>
+      <c r="C26" s="88"/>
+      <c r="D26" s="88"/>
+      <c r="E26" s="88"/>
+      <c r="F26" s="88"/>
+      <c r="G26" s="89"/>
       <c r="H26" s="23"/>
       <c r="I26" s="23"/>
       <c r="J26" s="23"/>
@@ -2291,63 +2294,65 @@
       <c r="A45" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="B45" s="73" t="s">
+      <c r="B45" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="C45" s="75" t="s">
+      <c r="C45" s="81" t="s">
         <v>91</v>
       </c>
-      <c r="D45" s="76"/>
-      <c r="E45" s="76"/>
-      <c r="F45" s="76"/>
-      <c r="G45" s="77"/>
+      <c r="D45" s="82"/>
+      <c r="E45" s="82"/>
+      <c r="F45" s="82"/>
+      <c r="G45" s="83"/>
     </row>
     <row r="46" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="84" t="s">
+      <c r="A46" s="90" t="s">
         <v>86</v>
       </c>
-      <c r="B46" s="74"/>
-      <c r="C46" s="78"/>
-      <c r="D46" s="79"/>
-      <c r="E46" s="79"/>
-      <c r="F46" s="79"/>
-      <c r="G46" s="80"/>
+      <c r="B46" s="80"/>
+      <c r="C46" s="84"/>
+      <c r="D46" s="85"/>
+      <c r="E46" s="85"/>
+      <c r="F46" s="85"/>
+      <c r="G46" s="86"/>
     </row>
     <row r="47" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="85"/>
-      <c r="B47" s="73" t="s">
+      <c r="A47" s="91"/>
+      <c r="B47" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="C47" s="75" t="s">
-        <v>92</v>
-      </c>
-      <c r="D47" s="76"/>
-      <c r="E47" s="76"/>
-      <c r="F47" s="76"/>
-      <c r="G47" s="77"/>
+      <c r="C47" s="81" t="s">
+        <v>93</v>
+      </c>
+      <c r="D47" s="82" t="s">
+        <v>94</v>
+      </c>
+      <c r="E47" s="82"/>
+      <c r="F47" s="82"/>
+      <c r="G47" s="83"/>
     </row>
     <row r="48" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="B48" s="74"/>
-      <c r="C48" s="78"/>
-      <c r="D48" s="79"/>
-      <c r="E48" s="79"/>
-      <c r="F48" s="79"/>
-      <c r="G48" s="80"/>
+      <c r="B48" s="80"/>
+      <c r="C48" s="84"/>
+      <c r="D48" s="85"/>
+      <c r="E48" s="85"/>
+      <c r="F48" s="85"/>
+      <c r="G48" s="86"/>
     </row>
     <row r="49" spans="2:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="C49" s="67" t="s">
-        <v>93</v>
-      </c>
-      <c r="D49" s="68"/>
-      <c r="E49" s="68"/>
-      <c r="F49" s="68"/>
-      <c r="G49" s="69"/>
+      <c r="C49" s="75" t="s">
+        <v>92</v>
+      </c>
+      <c r="D49" s="76"/>
+      <c r="E49" s="76"/>
+      <c r="F49" s="76"/>
+      <c r="G49" s="77"/>
     </row>
     <row r="51" spans="2:7" ht="13" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="52" spans="2:7" ht="13" thickBot="1" x14ac:dyDescent="0.3">
@@ -2375,7 +2380,18 @@
       <c r="G54" s="30"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="C45:G46"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="D47:G48"/>
+    <mergeCell ref="C47:C48"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E6:G6"/>
     <mergeCell ref="E11:G12"/>
@@ -2385,16 +2401,6 @@
     <mergeCell ref="D14:E15"/>
     <mergeCell ref="F14:G15"/>
     <mergeCell ref="D16:E16"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="C45:G46"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:G48"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <conditionalFormatting sqref="A18">
@@ -2497,17 +2503,28 @@
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<customXsn xmlns="http://schemas.microsoft.com/office/2006/metadata/customXsn">
-  <xsnLocation/>
-  <cached>True</cached>
-  <openByDefault>True</openByDefault>
-  <xsnScope/>
-</customXsn>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="34c87397-5fc1-491e-85e7-d6110dbe9cbd" ContentTypeId="0x010100CE50E52E7543470BBDD3827FE50C59CB" PreviousValue="false"/>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Owner xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105" xsi:nil="true"/>
+    <DocumentType xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105">Description</DocumentType>
+    <NokiaConfidentiality xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105">Nokia Internal Use</NokiaConfidentiality>
+    <HideFromDelve xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105">false</HideFromDelve>
+    <EXECUTE_x0020_Content xmlns="31aacdf4-fb95-42ec-80aa-6fc76e563ffe" xsi:nil="true"/>
+    <_dlc_DocId xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105">4NIMP5LIAM4P-487227298-104996</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105">
+      <Url>https://nokia.sharepoint.com/sites/FN_EXECUTE_Projects_01/19.PH.891566/_layouts/15/DocIdRedir.aspx?ID=4NIMP5LIAM4P-487227298-104996</Url>
+      <Description>4NIMP5LIAM4P-487227298-104996</Description>
+    </_dlc_DocIdUrl>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2727,29 +2744,18 @@
 </file>
 
 <file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Owner xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105" xsi:nil="true"/>
-    <DocumentType xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105">Description</DocumentType>
-    <NokiaConfidentiality xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105">Nokia Internal Use</NokiaConfidentiality>
-    <HideFromDelve xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105">false</HideFromDelve>
-    <EXECUTE_x0020_Content xmlns="31aacdf4-fb95-42ec-80aa-6fc76e563ffe" xsi:nil="true"/>
-    <_dlc_DocId xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105">4NIMP5LIAM4P-487227298-104996</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105">
-      <Url>https://nokia.sharepoint.com/sites/FN_EXECUTE_Projects_01/19.PH.891566/_layouts/15/DocIdRedir.aspx?ID=4NIMP5LIAM4P-487227298-104996</Url>
-      <Description>4NIMP5LIAM4P-487227298-104996</Description>
-    </_dlc_DocIdUrl>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="34c87397-5fc1-491e-85e7-d6110dbe9cbd" ContentTypeId="0x010100CE50E52E7543470BBDD3827FE50C59CB" PreviousValue="false"/>
 </file>
 
 <file path=customXml/item6.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<customXsn xmlns="http://schemas.microsoft.com/office/2006/metadata/customXsn">
+  <xsnLocation/>
+  <cached>True</cached>
+  <openByDefault>True</openByDefault>
+  <xsnScope/>
+</customXsn>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2761,17 +2767,20 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14AD1854-13FE-49B8-B5B1-8426C20F7669}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6B4300D-9EFA-4008-840F-6108E8E828B4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/customXsn"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A291274A-4EA0-4E57-B629-E0B27FF3F3C9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4695F569-C332-4377-B336-958B36C084BD}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="71c5aaf6-e6ce-465b-b873-5148d2a4c105"/>
+    <ds:schemaRef ds:uri="31aacdf4-fb95-42ec-80aa-6fc76e563ffe"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2796,20 +2805,17 @@
 </file>
 
 <file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4695F569-C332-4377-B336-958B36C084BD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A291274A-4EA0-4E57-B629-E0B27FF3F3C9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="71c5aaf6-e6ce-465b-b873-5148d2a4c105"/>
-    <ds:schemaRef ds:uri="31aacdf4-fb95-42ec-80aa-6fc76e563ffe"/>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps6.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6B4300D-9EFA-4008-840F-6108E8E828B4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14AD1854-13FE-49B8-B5B1-8426C20F7669}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/customXsn"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
